--- a/Lab03 - Data Acquisition/notebooks/API_notebook/task3_results.xlsx
+++ b/Lab03 - Data Acquisition/notebooks/API_notebook/task3_results.xlsx
@@ -484,7 +484,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3695</v>
+        <v>3693</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -505,7 +505,7 @@
         <v>31556</v>
       </c>
       <c r="C3" t="n">
-        <v>12108</v>
+        <v>12109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>194003</v>
+        <v>194002</v>
       </c>
       <c r="C5" t="n">
         <v>75213</v>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3571</v>
+        <v>3573</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>194003</v>
+        <v>194002</v>
       </c>
     </row>
     <row r="6">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>97960</v>
+        <v>97961</v>
       </c>
       <c r="C6" t="n">
         <v>27065</v>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18084</v>
+        <v>18088</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -608,13 +608,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>97960</v>
+        <v>97961</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Created at: 2026-03-04 20:10:14</t>
+          <t>Created at: 2026-03-04 21:17:23</t>
         </is>
       </c>
     </row>
